--- a/spark-cv/data/grants.xlsx
+++ b/spark-cv/data/grants.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A80E33B2-608B-41EA-8F14-5210C0EDA9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EBAD571-F0BC-4CD5-B1F9-E75F261959F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6630" yWindow="5025" windowWidth="21600" windowHeight="11505" xr2:uid="{2F3CED88-84B5-4249-9663-01EB28D3FE1D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21390" xr2:uid="{2F3CED88-84B5-4249-9663-01EB28D3FE1D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
   <si>
     <t>title</t>
   </si>
@@ -48,9 +48,6 @@
     <t>pi</t>
   </si>
   <si>
-    <t>Community, opportunity, and disparity in educational systems: Project CODES</t>
-  </si>
-  <si>
     <t>Principal Investigator</t>
   </si>
   <si>
@@ -129,13 +126,22 @@
     <t>Assessment of Water, Salt, Fire and  Land Management in Colorado River Basin using APEX</t>
   </si>
   <si>
-    <t>Bureau of Land Management</t>
-  </si>
-  <si>
     <t>Assistant Research Scientist</t>
   </si>
   <si>
     <t>Jaehak Jeong</t>
+  </si>
+  <si>
+    <t>Development of a Novel Water Quality Index Considering Impacts of Natural and Anthropogenic Hazards using APEX-MODFLOW</t>
+  </si>
+  <si>
+    <t>Environmental Protection Agency (EPA)</t>
+  </si>
+  <si>
+    <t>Bureau of Land Management (BLM)</t>
+  </si>
+  <si>
+    <t>Co-PI</t>
   </si>
 </sst>
 </file>
@@ -197,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
@@ -210,6 +216,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -536,7 +543,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -545,7 +552,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>2</v>
@@ -554,59 +561,61 @@
         <v>3</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K1" s="2" t="s">
+      <c r="M1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="G2" s="4">
-        <v>44378</v>
+        <v>44927</v>
       </c>
       <c r="H2" s="5">
-        <v>45838</v>
+        <v>46022</v>
       </c>
       <c r="I2" s="6">
-        <v>1699963</v>
+        <v>734219</v>
       </c>
       <c r="J2" s="2">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L2" s="2" t="b">
         <v>0</v>
@@ -618,33 +627,35 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G3" s="5">
-        <v>43922</v>
-      </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="2">
-        <v>48903.17</v>
+        <v>42856</v>
+      </c>
+      <c r="H3" s="5">
+        <v>44681</v>
+      </c>
+      <c r="I3" s="10">
+        <v>1004036</v>
       </c>
       <c r="J3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="2" t="b">
         <v>0</v>
@@ -688,22 +699,22 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="G6" s="8">
         <v>40344</v>
@@ -724,7 +735,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N6" s="2" t="b">
         <v>0</v>
@@ -732,17 +743,17 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>26</v>
-      </c>
       <c r="C7" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="1">
@@ -770,17 +781,17 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B8" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="1">

--- a/spark-cv/data/grants.xlsx
+++ b/spark-cv/data/grants.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25427"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EBAD571-F0BC-4CD5-B1F9-E75F261959F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA85E641-8450-4690-9F46-D363E86B0A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21390" xr2:uid="{2F3CED88-84B5-4249-9663-01EB28D3FE1D}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="38700" windowHeight="15555" xr2:uid="{2F3CED88-84B5-4249-9663-01EB28D3FE1D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -539,6 +539,8 @@
     <col min="4" max="4" width="15.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.75" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -612,10 +614,10 @@
         <v>734219</v>
       </c>
       <c r="J2" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K2" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L2" s="2" t="b">
         <v>0</v>
@@ -646,10 +648,10 @@
         <v>42856</v>
       </c>
       <c r="H3" s="5">
-        <v>44681</v>
+        <v>44804</v>
       </c>
       <c r="I3" s="10">
-        <v>1004036</v>
+        <v>2404036</v>
       </c>
       <c r="J3" s="2">
         <v>1</v>
@@ -674,7 +676,7 @@
       <c r="F4" s="2"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
-      <c r="I4" s="2"/>
+      <c r="I4" s="10"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>

--- a/spark-cv/data/grants.xlsx
+++ b/spark-cv/data/grants.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA85E641-8450-4690-9F46-D363E86B0A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC80F03F-B7F8-44B2-8787-6B7F7595A3D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="38700" windowHeight="15555" xr2:uid="{2F3CED88-84B5-4249-9663-01EB28D3FE1D}"/>
+    <workbookView xWindow="51480" yWindow="3300" windowWidth="29040" windowHeight="17790" xr2:uid="{2F3CED88-84B5-4249-9663-01EB28D3FE1D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="43">
   <si>
     <t>title</t>
   </si>
@@ -135,13 +135,34 @@
     <t>Development of a Novel Water Quality Index Considering Impacts of Natural and Anthropogenic Hazards using APEX-MODFLOW</t>
   </si>
   <si>
-    <t>Environmental Protection Agency (EPA)</t>
-  </si>
-  <si>
-    <t>Bureau of Land Management (BLM)</t>
-  </si>
-  <si>
     <t>Co-PI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development of a Carbon Dynamics Model for Predicting GHG Emission and Sequestration in Croplands   </t>
+  </si>
+  <si>
+    <t>Rural Development Administration (RDA), Korea</t>
+  </si>
+  <si>
+    <t>Development of DayCent Optimization framework with the Differential Evolution Adaptive Metropolis (DREAM) algorithm</t>
+  </si>
+  <si>
+    <t>Agoro Carbon Alliance, United States</t>
+  </si>
+  <si>
+    <t>Bureau of Land Management (BLM), United States</t>
+  </si>
+  <si>
+    <t>Environmental Protection Agency (EPA), United States</t>
+  </si>
+  <si>
+    <t>Post-Doctoral Associate</t>
+  </si>
+  <si>
+    <t>SWAT-MODFLOW modeling to support resilient development and return on investment analyses in the Cubango-Okavango River Basin (CORB)</t>
+  </si>
+  <si>
+    <t>The Nature Conservancy (TNC), United States</t>
   </si>
 </sst>
 </file>
@@ -203,20 +224,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -531,10 +551,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4605E665-D6A4-C749-961B-EF6BCFDB74F3}">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="86" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="81.5" customWidth="1"/>
     <col min="3" max="3" width="55.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.75" bestFit="1" customWidth="1"/>
@@ -544,282 +564,383 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" t="s">
         <v>22</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="3">
+        <v>44927</v>
+      </c>
+      <c r="H2" s="4">
+        <v>46022</v>
+      </c>
+      <c r="I2" s="5">
+        <v>734219</v>
+      </c>
+      <c r="J2">
+        <v>0.5</v>
+      </c>
+      <c r="K2">
+        <v>0.5</v>
+      </c>
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G3" s="3">
         <v>44927</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H3" s="4">
         <v>46022</v>
       </c>
-      <c r="I2" s="6">
-        <v>734219</v>
-      </c>
-      <c r="J2" s="2">
+      <c r="I3" s="5">
+        <v>240000</v>
+      </c>
+      <c r="J3">
+        <v>0.1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="4">
+        <v>42856</v>
+      </c>
+      <c r="H4" s="4">
+        <v>45169</v>
+      </c>
+      <c r="I4" s="9">
+        <v>2404036</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="9"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="4">
+        <v>44927</v>
+      </c>
+      <c r="H6" s="4">
+        <v>45016</v>
+      </c>
+      <c r="I6" s="9">
+        <v>25000</v>
+      </c>
+      <c r="J6">
+        <v>0.1</v>
+      </c>
+      <c r="K6">
         <v>0.5</v>
       </c>
-      <c r="K2" s="2">
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="4">
+        <v>43922</v>
+      </c>
+      <c r="H7" s="4">
+        <v>44316</v>
+      </c>
+      <c r="I7" s="9">
+        <v>30000</v>
+      </c>
+      <c r="J7">
+        <v>0.1</v>
+      </c>
+      <c r="K7">
         <v>0.5</v>
       </c>
-      <c r="L2" s="2" t="b">
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+      <c r="N7" t="b">
         <v>0</v>
       </c>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="5">
-        <v>42856</v>
-      </c>
-      <c r="H3" s="5">
-        <v>44804</v>
-      </c>
-      <c r="I3" s="10">
-        <v>2404036</v>
-      </c>
-      <c r="J3" s="2">
-        <v>1</v>
-      </c>
-      <c r="K3" s="2">
-        <v>1</v>
-      </c>
-      <c r="L3" s="2" t="b">
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="7">
+        <v>40344</v>
+      </c>
+      <c r="H10" s="7">
+        <v>41804</v>
+      </c>
+      <c r="I10">
+        <v>1631403</v>
+      </c>
+      <c r="J10">
+        <v>0.51</v>
+      </c>
+      <c r="K10">
+        <v>0.61</v>
+      </c>
+      <c r="L10" t="b">
         <v>0</v>
       </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2" t="b">
+      <c r="M10" t="s">
+        <v>20</v>
+      </c>
+      <c r="N10" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="3" t="s">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="8">
-        <v>40344</v>
-      </c>
-      <c r="H6" s="8">
-        <v>41804</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1631403</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0.51</v>
-      </c>
-      <c r="K6" s="2">
-        <v>0.61</v>
-      </c>
-      <c r="L6" s="2" t="b">
+      <c r="E11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G11" s="1">
+        <v>44075</v>
+      </c>
+      <c r="H11" s="1">
+        <v>44439</v>
+      </c>
+      <c r="I11">
+        <v>1399163</v>
+      </c>
+      <c r="J11">
+        <v>0.35</v>
+      </c>
+      <c r="K11">
+        <v>0.35</v>
+      </c>
+      <c r="L11" t="b">
         <v>0</v>
       </c>
-      <c r="M6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="N6" s="2" t="b">
+      <c r="N11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G12" s="1">
+        <v>42736</v>
+      </c>
+      <c r="H12" s="3">
+        <v>43100</v>
+      </c>
+      <c r="I12">
+        <v>19946</v>
+      </c>
+      <c r="J12">
+        <v>0.19</v>
+      </c>
+      <c r="K12">
+        <v>0.19</v>
+      </c>
+      <c r="L12" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="1">
-        <v>44075</v>
-      </c>
-      <c r="H7" s="1">
-        <v>44439</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1399163</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0.35</v>
-      </c>
-      <c r="K7" s="2">
-        <v>0.35</v>
-      </c>
-      <c r="L7" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="1">
-        <v>42736</v>
-      </c>
-      <c r="H8" s="4">
-        <v>43100</v>
-      </c>
-      <c r="I8" s="2">
-        <v>19946</v>
-      </c>
-      <c r="J8" s="2">
-        <v>0.19</v>
-      </c>
-      <c r="K8" s="2">
-        <v>0.19</v>
-      </c>
-      <c r="L8" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2" t="b">
+      <c r="N12" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/spark-cv/data/grants.xlsx
+++ b/spark-cv/data/grants.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC80F03F-B7F8-44B2-8787-6B7F7595A3D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E760AA-A054-48C1-A110-156288DB140D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51480" yWindow="3300" windowWidth="29040" windowHeight="17790" xr2:uid="{2F3CED88-84B5-4249-9663-01EB28D3FE1D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="27240" windowHeight="16680" xr2:uid="{2F3CED88-84B5-4249-9663-01EB28D3FE1D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="52">
   <si>
     <t>title</t>
   </si>
@@ -138,9 +138,6 @@
     <t>Co-PI</t>
   </si>
   <si>
-    <t xml:space="preserve">Development of a Carbon Dynamics Model for Predicting GHG Emission and Sequestration in Croplands   </t>
-  </si>
-  <si>
     <t>Rural Development Administration (RDA), Korea</t>
   </si>
   <si>
@@ -156,13 +153,43 @@
     <t>Environmental Protection Agency (EPA), United States</t>
   </si>
   <si>
-    <t>Post-Doctoral Associate</t>
-  </si>
-  <si>
     <t>SWAT-MODFLOW modeling to support resilient development and return on investment analyses in the Cubango-Okavango River Basin (CORB)</t>
   </si>
   <si>
     <t>The Nature Conservancy (TNC), United States</t>
+  </si>
+  <si>
+    <t>Seonggyu Park</t>
+  </si>
+  <si>
+    <t>PI</t>
+  </si>
+  <si>
+    <t>Climate-Smart Agricultural Water Resource Adaptation Platform</t>
+  </si>
+  <si>
+    <t>Rural Development Administration of the Republic of Korea</t>
+  </si>
+  <si>
+    <t>Soil Health Demonstrations to Increase Regenerative Agricultural Intensification in Southern High Plains</t>
+  </si>
+  <si>
+    <t>USDA-Natural Resources Conservation Services</t>
+  </si>
+  <si>
+    <t>Joseph Burke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development of Catchment-scale Computational Model for Assessing Climate Change Impact and Risks on Water ­Environment in Agriculture </t>
+  </si>
+  <si>
+    <t>Koksilah SWAT-MODFLOW model optimization</t>
+  </si>
+  <si>
+    <t>https://www.koksilahwater.ca/getinvolved</t>
+  </si>
+  <si>
+    <t>University of Victoria, Canada</t>
   </si>
 </sst>
 </file>
@@ -172,7 +199,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -203,6 +230,14 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -221,10 +256,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
@@ -237,8 +273,10 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -551,16 +589,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4605E665-D6A4-C749-961B-EF6BCFDB74F3}">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="81.5" customWidth="1"/>
+    <col min="2" max="2" width="114.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.75" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="49.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -611,36 +650,32 @@
       <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" s="2"/>
+      <c r="B2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" t="s">
+        <v>46</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>31</v>
+      <c r="F2" t="s">
+        <v>47</v>
       </c>
       <c r="G2" s="3">
-        <v>44927</v>
-      </c>
-      <c r="H2" s="4">
-        <v>46022</v>
-      </c>
-      <c r="I2" s="5">
-        <v>734219</v>
+        <v>45444</v>
+      </c>
+      <c r="H2" s="3">
+        <v>47269</v>
+      </c>
+      <c r="I2" s="9">
+        <v>4999387</v>
       </c>
       <c r="J2">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="K2">
-        <v>0.5</v>
-      </c>
-      <c r="L2" t="b">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -648,17 +683,17 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>31</v>
@@ -670,104 +705,107 @@
         <v>46022</v>
       </c>
       <c r="I3" s="5">
-        <v>240000</v>
+        <v>734219</v>
       </c>
       <c r="J3">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="5"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="3">
+        <v>45231</v>
+      </c>
+      <c r="H5" s="4">
+        <v>46022</v>
+      </c>
+      <c r="I5" s="5">
+        <v>540000</v>
+      </c>
+      <c r="J5">
+        <v>0.5</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="4">
-        <v>42856</v>
-      </c>
-      <c r="H4" s="4">
-        <v>45169</v>
-      </c>
-      <c r="I4" s="9">
-        <v>2404036</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4" t="b">
-        <v>1</v>
-      </c>
-      <c r="N4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="9"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="4">
-        <v>44927</v>
+        <v>41</v>
+      </c>
+      <c r="G6" s="3">
+        <v>45231</v>
       </c>
       <c r="H6" s="4">
-        <v>45016</v>
-      </c>
-      <c r="I6" s="9">
-        <v>25000</v>
+        <v>45382</v>
+      </c>
+      <c r="I6" s="5">
+        <v>20000</v>
       </c>
       <c r="J6">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="K6">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L6" t="b">
         <v>1</v>
+      </c>
+      <c r="M6" s="10" t="s">
+        <v>50</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -775,32 +813,32 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="4">
-        <v>43922</v>
+      <c r="G7" s="3">
+        <v>44927</v>
       </c>
       <c r="H7" s="4">
-        <v>44316</v>
-      </c>
-      <c r="I7" s="9">
-        <v>30000</v>
+        <v>46022</v>
+      </c>
+      <c r="I7" s="5">
+        <v>540000</v>
       </c>
       <c r="J7">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="K7">
         <v>0.5</v>
@@ -817,53 +855,84 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
-      <c r="G8" s="4"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="3"/>
       <c r="H8" s="4"/>
+      <c r="I8" s="5"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="E9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="4">
+        <v>42856</v>
+      </c>
+      <c r="H9" s="4">
+        <v>45169</v>
+      </c>
+      <c r="I9" s="9">
+        <v>2404036</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
       <c r="B10" s="2" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>11</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="7">
-        <v>40344</v>
-      </c>
-      <c r="H10" s="7">
-        <v>41804</v>
-      </c>
-      <c r="I10">
-        <v>1631403</v>
+        <v>33</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="4">
+        <v>44927</v>
+      </c>
+      <c r="H10" s="4">
+        <v>45016</v>
+      </c>
+      <c r="I10" s="9">
+        <v>25000</v>
       </c>
       <c r="J10">
-        <v>0.51</v>
+        <v>0.1</v>
       </c>
       <c r="K10">
-        <v>0.61</v>
+        <v>0.5</v>
       </c>
       <c r="L10" t="b">
-        <v>0</v>
-      </c>
-      <c r="M10" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
@@ -871,76 +940,175 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="4">
+        <v>43922</v>
+      </c>
+      <c r="H11" s="4">
+        <v>44316</v>
+      </c>
+      <c r="I11" s="9">
+        <v>30000</v>
+      </c>
+      <c r="J11">
+        <v>0.1</v>
+      </c>
+      <c r="K11">
+        <v>0.5</v>
+      </c>
+      <c r="L11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="7">
+        <v>40344</v>
+      </c>
+      <c r="H14" s="7">
+        <v>41804</v>
+      </c>
+      <c r="I14">
+        <v>1631403</v>
+      </c>
+      <c r="J14">
+        <v>0.51</v>
+      </c>
+      <c r="K14">
+        <v>0.61</v>
+      </c>
+      <c r="L14" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" t="s">
+        <v>20</v>
+      </c>
+      <c r="N14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B15" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G15" s="1">
         <v>44075</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H15" s="1">
         <v>44439</v>
       </c>
-      <c r="I11">
+      <c r="I15">
         <v>1399163</v>
       </c>
-      <c r="J11">
+      <c r="J15">
         <v>0.35</v>
       </c>
-      <c r="K11">
+      <c r="K15">
         <v>0.35</v>
       </c>
-      <c r="L11" t="b">
+      <c r="L15" t="b">
         <v>0</v>
       </c>
-      <c r="N11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="N15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B16" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G16" s="1">
         <v>42736</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H16" s="3">
         <v>43100</v>
       </c>
-      <c r="I12">
+      <c r="I16">
         <v>19946</v>
       </c>
-      <c r="J12">
+      <c r="J16">
         <v>0.19</v>
       </c>
-      <c r="K12">
+      <c r="K16">
         <v>0.19</v>
       </c>
-      <c r="L12" t="b">
+      <c r="L16" t="b">
         <v>0</v>
       </c>
-      <c r="N12" t="b">
+      <c r="N16" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="M6" r:id="rId1" xr:uid="{93C429AB-1EDF-40B9-B2B5-A03AA2D3B352}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/spark-cv/data/grants.xlsx
+++ b/spark-cv/data/grants.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E760AA-A054-48C1-A110-156288DB140D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1374FA25-523A-4579-BA96-47B2D1176181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="27240" windowHeight="16680" xr2:uid="{2F3CED88-84B5-4249-9663-01EB28D3FE1D}"/>
+    <workbookView xWindow="3075" yWindow="3075" windowWidth="43200" windowHeight="17355" xr2:uid="{2F3CED88-84B5-4249-9663-01EB28D3FE1D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
